--- a/MBA BA 2026-28 Term I Schedule.xlsx
+++ b/MBA BA 2026-28 Term I Schedule.xlsx
@@ -374,81 +374,81 @@
     <t>MComp - (Prof. Manish Kumar) presentation</t>
   </si>
   <si>
+    <t>OBD - 13 (Prof. Shubhi Gupta)</t>
+  </si>
+  <si>
+    <t>OBD - 14 (Prof. Shubhi Gupta)</t>
+  </si>
+  <si>
     <t>DS-I - 13 (Prof. Kaustov Chakraborty)</t>
   </si>
   <si>
+    <t>IBA - 1( Prof. Ashish Rathore)</t>
+  </si>
+  <si>
+    <t>MM -13 ( Prof. Chhavi Gupta)</t>
+  </si>
+  <si>
+    <t>FRA- 14 (Prof. Meena Bhatia)</t>
+  </si>
+  <si>
+    <t>MC - 13 (Prof Kakoli Sen)</t>
+  </si>
+  <si>
+    <t>MC - 14 (Prof Kakoli Sen)</t>
+  </si>
+  <si>
+    <t>FRA- 15 (Prof. Meena Bhatia)</t>
+  </si>
+  <si>
+    <t>Milad-un-Nabi or Id-e-Milad</t>
+  </si>
+  <si>
+    <t>IBA -2 ( Prof. Ashish Rathore)</t>
+  </si>
+  <si>
+    <t>MM -14 ( Prof. Chhavi Gupta)</t>
+  </si>
+  <si>
+    <t>FRA- 16 (Prof. Meena Bhatia)</t>
+  </si>
+  <si>
+    <t>MC - 15 (Prof Kakoli Sen)</t>
+  </si>
+  <si>
+    <t>MC - 16 (Prof Kakoli Sen)</t>
+  </si>
+  <si>
+    <t>BE-15 (Prof Hemachandra Pradhan)</t>
+  </si>
+  <si>
+    <t>MM -15 ( Prof. Chhavi Gupta)</t>
+  </si>
+  <si>
+    <t>FRA- 17 (Prof. Meena Bhatia)</t>
+  </si>
+  <si>
+    <t>BE-16 (Prof Hemachandra Pradhan)</t>
+  </si>
+  <si>
+    <t>IBA - 3 ( Prof. Ashish Rathore)</t>
+  </si>
+  <si>
+    <t>BE-17 (Prof Hemachandra Pradhan)</t>
+  </si>
+  <si>
+    <t>FRA- 18 (Prof. Meena Bhatia)</t>
+  </si>
+  <si>
+    <t>MM -16 ( Prof. Chhavi Gupta)</t>
+  </si>
+  <si>
     <t>DS-I - 14 (Prof. Kaustov Chakraborty)</t>
   </si>
   <si>
-    <t>OBD - 13 (Prof. Shubhi Gupta)</t>
-  </si>
-  <si>
-    <t>IBA - 1( Prof. Ashish Rathore)</t>
-  </si>
-  <si>
-    <t>MM -13 ( Prof. Chhavi Gupta)</t>
-  </si>
-  <si>
-    <t>FRA- 14 (Prof. Meena Bhatia)</t>
-  </si>
-  <si>
-    <t>MC - 13 (Prof Kakoli Sen)</t>
-  </si>
-  <si>
-    <t>MC - 14 (Prof Kakoli Sen)</t>
-  </si>
-  <si>
-    <t>FRA- 15 (Prof. Meena Bhatia)</t>
-  </si>
-  <si>
-    <t>Milad-un-Nabi or Id-e-Milad</t>
-  </si>
-  <si>
-    <t>IBA -2 ( Prof. Ashish Rathore)</t>
-  </si>
-  <si>
-    <t>MM -14 ( Prof. Chhavi Gupta)</t>
-  </si>
-  <si>
-    <t>FRA- 16 (Prof. Meena Bhatia)</t>
-  </si>
-  <si>
-    <t>MC - 15 (Prof Kakoli Sen)</t>
-  </si>
-  <si>
-    <t>MC - 16 (Prof Kakoli Sen)</t>
-  </si>
-  <si>
-    <t>BE-15 (Prof Hemachandra Pradhan)</t>
-  </si>
-  <si>
-    <t>MM -15 ( Prof. Chhavi Gupta)</t>
-  </si>
-  <si>
-    <t>FRA- 17 (Prof. Meena Bhatia)</t>
-  </si>
-  <si>
-    <t>BE-16 (Prof Hemachandra Pradhan)</t>
-  </si>
-  <si>
-    <t>IBA - 3 ( Prof. Ashish Rathore)</t>
-  </si>
-  <si>
-    <t>BE-17 (Prof Hemachandra Pradhan)</t>
-  </si>
-  <si>
-    <t>FRA- 18 (Prof. Meena Bhatia)</t>
-  </si>
-  <si>
-    <t>MM -16 ( Prof. Chhavi Gupta)</t>
-  </si>
-  <si>
     <t>DS-I - 15 (Prof. Kaustov Chakraborty)</t>
   </si>
   <si>
-    <t>OBD - 14 (Prof. Shubhi Gupta)</t>
-  </si>
-  <si>
     <t>FRA- 19 (Prof. Meena Bhatia)</t>
   </si>
   <si>
@@ -464,87 +464,87 @@
     <t>DS-I - 17 (Prof. Kaustov Chakraborty)</t>
   </si>
   <si>
+    <t>MM -17 ( Prof. Chhavi Gupta)</t>
+  </si>
+  <si>
+    <t>IBA - 4 ( Prof. Ashish Rathore)</t>
+  </si>
+  <si>
+    <t>MM -18 ( Prof. Chhavi Gupta)</t>
+  </si>
+  <si>
+    <t>BE-18 (Prof Hemachandra Pradhan)</t>
+  </si>
+  <si>
+    <t>MM -19 ( Prof. Chhavi Gupta)</t>
+  </si>
+  <si>
+    <t>MM -20 ( Prof. Chhavi Gupta)</t>
+  </si>
+  <si>
+    <t>IBA - 5 ( Prof. Ashish Rathore)</t>
+  </si>
+  <si>
+    <t>FRA- 20 (Prof. Meena Bhatia)</t>
+  </si>
+  <si>
+    <t>BE-19 (Prof Hemachandra Pradhan)</t>
+  </si>
+  <si>
+    <t>BE-20 (Prof Hemachandra Pradhan)</t>
+  </si>
+  <si>
+    <t>IBA - 6 ( Prof. Ashish Rathore)</t>
+  </si>
+  <si>
+    <t>IBA - 7 ( Prof. Ashish Rathore)</t>
+  </si>
+  <si>
+    <t>MC - 17 (Prof Kakoli Sen)</t>
+  </si>
+  <si>
+    <t>IBA - 8 ( Prof. Ashish Rathore)</t>
+  </si>
+  <si>
+    <t>MC - 18 (Prof Kakoli Sen)</t>
+  </si>
+  <si>
+    <t>DS-I - 18(Prof. Kaustov Chakraborty)</t>
+  </si>
+  <si>
     <t>OBD - 17 (Prof. Shubhi Gupta)</t>
   </si>
   <si>
-    <t>MM -17 ( Prof. Chhavi Gupta)</t>
-  </si>
-  <si>
-    <t>IBA - 4 ( Prof. Ashish Rathore)</t>
-  </si>
-  <si>
-    <t>MM -18 ( Prof. Chhavi Gupta)</t>
-  </si>
-  <si>
-    <t>BE-18 (Prof Hemachandra Pradhan)</t>
-  </si>
-  <si>
-    <t>MM -19 ( Prof. Chhavi Gupta)</t>
-  </si>
-  <si>
-    <t>MM -20 ( Prof. Chhavi Gupta)</t>
-  </si>
-  <si>
-    <t>IBA - 5 ( Prof. Ashish Rathore)</t>
-  </si>
-  <si>
-    <t>FRA- 20 (Prof. Meena Bhatia)</t>
-  </si>
-  <si>
-    <t>BE-19 (Prof Hemachandra Pradhan)</t>
-  </si>
-  <si>
-    <t>BE-20 (Prof Hemachandra Pradhan)</t>
-  </si>
-  <si>
-    <t>IBA - 6 ( Prof. Ashish Rathore)</t>
-  </si>
-  <si>
-    <t>IBA - 7 ( Prof. Ashish Rathore)</t>
-  </si>
-  <si>
-    <t>MC - 17 (Prof Kakoli Sen)</t>
-  </si>
-  <si>
-    <t>IBA - 8 ( Prof. Ashish Rathore)</t>
-  </si>
-  <si>
-    <t>MC - 18 (Prof Kakoli Sen)</t>
-  </si>
-  <si>
-    <t>DS-I - 18(Prof. Kaustov Chakraborty)</t>
+    <t>DS-I - 19 (Prof. Kaustov Chakraborty)</t>
   </si>
   <si>
     <t>OBD - 18 (Prof. Shubhi Gupta)</t>
   </si>
   <si>
-    <t>DS-I - 19 (Prof. Kaustov Chakraborty)</t>
+    <t>MC - 19 (Prof Kakoli Sen)</t>
+  </si>
+  <si>
+    <t>DS-I - 20 (Prof. Kaustov Chakraborty)</t>
   </si>
   <si>
     <t>OBD - 19 (Prof. Shubhi Gupta)</t>
   </si>
   <si>
-    <t>MC - 19 (Prof Kakoli Sen)</t>
-  </si>
-  <si>
-    <t>DS-I - 20 (Prof. Kaustov Chakraborty)</t>
+    <t>IBA - 9 ( Prof. Ashish Rathore)</t>
+  </si>
+  <si>
+    <t>MC AI Case Discussion</t>
+  </si>
+  <si>
+    <t>IBA - 10 ( Prof. Ashish Rathore)</t>
+  </si>
+  <si>
+    <t>MC - 20 (Prof Kakoli Sen)</t>
   </si>
   <si>
     <t>OBD - 20 (Prof. Shubhi Gupta)</t>
   </si>
   <si>
-    <t>IBA - 9 ( Prof. Ashish Rathore)</t>
-  </si>
-  <si>
-    <t>MC AI Case Discussion</t>
-  </si>
-  <si>
-    <t>IBA - 10 ( Prof. Ashish Rathore)</t>
-  </si>
-  <si>
-    <t>MC - 20 (Prof Kakoli Sen)</t>
-  </si>
-  <si>
     <t>END TERM</t>
   </si>
   <si>
@@ -587,7 +587,7 @@
     <t>MBA-BA101</t>
   </si>
   <si>
-    <t xml:space="preserve">Prof.Kaushik Bhattacharya and Prof Hemachandra Padhan </t>
+    <t xml:space="preserve">Prof. Kaushik Bhattacharya and Prof Hemachandra Padhan </t>
   </si>
   <si>
     <t>kbhattacharya@iiml.ac.in
@@ -911,13 +911,13 @@
     </xf>
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -956,19 +956,19 @@
     <xf borderId="5" fillId="9" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -977,40 +977,40 @@
     <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="12" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="5" fillId="13" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="13" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="13" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="13" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="13" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1019,15 +1019,15 @@
     <xf borderId="5" fillId="15" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="15" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="15" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="15" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="15" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="9" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="9" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1039,118 +1039,118 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="15" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="15" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="15" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="15" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="14" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="14" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="14" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="14" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="14" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="14" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2190,14 +2190,14 @@
       <c r="B44" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="25" t="s">
         <v>112</v>
       </c>
       <c r="E44" s="14"/>
-      <c r="F44" s="25" t="s">
+      <c r="F44" s="18" t="s">
         <v>113</v>
       </c>
       <c r="G44" s="13" t="s">
@@ -2292,7 +2292,6 @@
       <c r="F49" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G49" s="16"/>
       <c r="J49" s="1"/>
     </row>
     <row r="50">
@@ -2374,7 +2373,6 @@
         <v>130</v>
       </c>
       <c r="E54" s="14"/>
-      <c r="G54" s="16"/>
       <c r="J54" s="1"/>
     </row>
     <row r="55">
@@ -2407,7 +2405,7 @@
       <c r="C56" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D56" s="25" t="s">
+      <c r="D56" s="18" t="s">
         <v>135</v>
       </c>
       <c r="E56" s="14"/>
@@ -2447,12 +2445,9 @@
       <c r="C58" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="D58" s="25" t="s">
-        <v>141</v>
-      </c>
       <c r="E58" s="14"/>
       <c r="F58" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G58" s="16"/>
       <c r="J58" s="1"/>
@@ -2479,10 +2474,10 @@
         <v>31</v>
       </c>
       <c r="C60" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="D60" s="15" t="s">
         <v>143</v>
-      </c>
-      <c r="D60" s="15" t="s">
-        <v>144</v>
       </c>
       <c r="E60" s="14"/>
       <c r="G60" s="16"/>
@@ -2510,14 +2505,14 @@
         <v>16</v>
       </c>
       <c r="C62" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="D62" s="15" t="s">
         <v>145</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>146</v>
       </c>
       <c r="E62" s="14"/>
       <c r="F62" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G62" s="16"/>
       <c r="J62" s="1"/>
@@ -2530,14 +2525,14 @@
         <v>20</v>
       </c>
       <c r="C63" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="D63" s="12" t="s">
         <v>148</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>149</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="37" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G63" s="16"/>
       <c r="J63" s="1"/>
@@ -2550,10 +2545,10 @@
         <v>24</v>
       </c>
       <c r="C64" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="D64" s="39" t="s">
         <v>151</v>
-      </c>
-      <c r="D64" s="39" t="s">
-        <v>152</v>
       </c>
       <c r="E64" s="14"/>
       <c r="F64" s="16"/>
@@ -2608,10 +2603,10 @@
         <v>31</v>
       </c>
       <c r="C67" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="D67" s="17" t="s">
         <v>153</v>
-      </c>
-      <c r="D67" s="17" t="s">
-        <v>154</v>
       </c>
       <c r="E67" s="14"/>
       <c r="F67" s="8"/>
@@ -2626,13 +2621,12 @@
         <v>12</v>
       </c>
       <c r="C68" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="D68" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="D68" s="17" t="s">
-        <v>156</v>
-      </c>
       <c r="E68" s="14"/>
-      <c r="F68" s="16"/>
       <c r="G68" s="16"/>
       <c r="J68" s="1"/>
     </row>
@@ -2644,10 +2638,10 @@
         <v>16</v>
       </c>
       <c r="C69" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="D69" s="25" t="s">
         <v>157</v>
-      </c>
-      <c r="D69" s="25" t="s">
-        <v>158</v>
       </c>
       <c r="E69" s="14"/>
       <c r="F69" s="8"/>
@@ -2662,14 +2656,14 @@
         <v>20</v>
       </c>
       <c r="C70" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="D70" s="25" t="s">
         <v>159</v>
-      </c>
-      <c r="D70" s="25" t="s">
-        <v>160</v>
       </c>
       <c r="E70" s="14"/>
       <c r="F70" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G70" s="16"/>
       <c r="J70" s="1"/>
@@ -2682,17 +2676,17 @@
         <v>24</v>
       </c>
       <c r="C71" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="D71" s="25" t="s">
         <v>162</v>
-      </c>
-      <c r="D71" s="25" t="s">
-        <v>163</v>
       </c>
       <c r="E71" s="14"/>
       <c r="F71" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="G71" s="17" t="s">
         <v>164</v>
-      </c>
-      <c r="G71" s="17" t="s">
-        <v>165</v>
       </c>
       <c r="J71" s="1"/>
     </row>
@@ -2704,13 +2698,15 @@
         <v>27</v>
       </c>
       <c r="C72" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="D72" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="E72" s="14"/>
+      <c r="F72" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="E72" s="14"/>
-      <c r="F72" s="16"/>
       <c r="G72" s="16"/>
       <c r="J72" s="1"/>
     </row>
